--- a/data/excel/emae_letras.xlsx
+++ b/data/excel/emae_letras.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q272"/>
+  <dimension ref="A1:Q273"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -12095,7 +12095,7 @@
         <v>134.5108294690881</v>
       </c>
       <c r="F220" t="n">
-        <v>146.0160006277402</v>
+        <v>146.0160006277391</v>
       </c>
       <c r="G220" t="n">
         <v>156.3378844148655</v>
@@ -13049,7 +13049,7 @@
         <v>133.0817362197774</v>
       </c>
       <c r="F238" t="n">
-        <v>144.1353499917185</v>
+        <v>144.1353499917196</v>
       </c>
       <c r="G238" t="n">
         <v>159.9226843603715</v>
@@ -14521,52 +14521,52 @@
         <v>46023</v>
       </c>
       <c r="B266" t="n">
-        <v>114.4548561614751</v>
+        <v>113.8596467729688</v>
       </c>
       <c r="C266" t="n">
-        <v>229.4333908984985</v>
+        <v>229.4319574876168</v>
       </c>
       <c r="D266" t="n">
-        <v>135.273994032279</v>
+        <v>135.2729380350471</v>
       </c>
       <c r="E266" t="n">
-        <v>104.2006660617906</v>
+        <v>104.1691666671136</v>
       </c>
       <c r="F266" t="n">
-        <v>162.3130498442855</v>
+        <v>162.3117175841722</v>
       </c>
       <c r="G266" t="n">
-        <v>133.1972369304629</v>
+        <v>133.2008005541675</v>
       </c>
       <c r="H266" t="n">
-        <v>146.4258295621789</v>
+        <v>146.4123362741914</v>
       </c>
       <c r="I266" t="n">
-        <v>199.4955554742106</v>
+        <v>199.3319756696513</v>
       </c>
       <c r="J266" t="n">
-        <v>186.7776422005339</v>
+        <v>186.701854429655</v>
       </c>
       <c r="K266" t="n">
-        <v>198.7166118453509</v>
+        <v>198.7295886271345</v>
       </c>
       <c r="L266" t="n">
-        <v>153.6706522001886</v>
+        <v>153.676362047342</v>
       </c>
       <c r="M266" t="n">
         <v>160.6868353127149</v>
       </c>
       <c r="N266" t="n">
-        <v>167.3704249932719</v>
+        <v>167.4042822423986</v>
       </c>
       <c r="O266" t="n">
-        <v>187.2836758547118</v>
+        <v>187.329546751618</v>
       </c>
       <c r="P266" t="n">
-        <v>141.455080086122</v>
+        <v>141.5175447739272</v>
       </c>
       <c r="Q266" t="n">
-        <v>186.7469851222559</v>
+        <v>186.729009171829</v>
       </c>
     </row>
     <row r="267">
@@ -14574,52 +14574,52 @@
         <v>46054</v>
       </c>
       <c r="B267" t="n">
-        <v>81.87527015949428</v>
+        <v>81.58174170315169</v>
       </c>
       <c r="C267" t="n">
-        <v>252.6499510141572</v>
+        <v>252.6498460847773</v>
       </c>
       <c r="D267" t="n">
-        <v>121.5633374131426</v>
+        <v>121.562972975731</v>
       </c>
       <c r="E267" t="n">
-        <v>98.61520857107608</v>
+        <v>98.60704761400508</v>
       </c>
       <c r="F267" t="n">
-        <v>147.2242375588131</v>
+        <v>147.2239508462717</v>
       </c>
       <c r="G267" t="n">
-        <v>130.2408472520369</v>
+        <v>130.2929605339996</v>
       </c>
       <c r="H267" t="n">
-        <v>143.75010048096</v>
+        <v>143.7759594227877</v>
       </c>
       <c r="I267" t="n">
-        <v>192.4957991422613</v>
+        <v>192.5110893817951</v>
       </c>
       <c r="J267" t="n">
-        <v>175.5080113370782</v>
+        <v>175.5387084234417</v>
       </c>
       <c r="K267" t="n">
-        <v>187.5927343097088</v>
+        <v>187.6037300454419</v>
       </c>
       <c r="L267" t="n">
-        <v>153.6011407425851</v>
+        <v>153.6092933828685</v>
       </c>
       <c r="M267" t="n">
         <v>160.7108468649468</v>
       </c>
       <c r="N267" t="n">
-        <v>169.0779546103857</v>
+        <v>169.0796227163826</v>
       </c>
       <c r="O267" t="n">
-        <v>176.945614738947</v>
+        <v>176.9810286324323</v>
       </c>
       <c r="P267" t="n">
-        <v>139.3013657728037</v>
+        <v>139.26897974256</v>
       </c>
       <c r="Q267" t="n">
-        <v>161.8719770067183</v>
+        <v>161.7553320266139</v>
       </c>
     </row>
     <row r="268">
@@ -14627,52 +14627,52 @@
         <v>46082</v>
       </c>
       <c r="B268" t="n">
-        <v>180.5063261987838</v>
+        <v>181.3950640436327</v>
       </c>
       <c r="C268" t="n">
-        <v>169.0056304095275</v>
+        <v>169.007168749789</v>
       </c>
       <c r="D268" t="n">
-        <v>136.2206129451463</v>
+        <v>136.2220333797903</v>
       </c>
       <c r="E268" t="n">
-        <v>121.9389870006395</v>
+        <v>121.9786473523871</v>
       </c>
       <c r="F268" t="n">
-        <v>154.7391083281458</v>
+        <v>154.7407273007994</v>
       </c>
       <c r="G268" t="n">
-        <v>143.0183003411241</v>
+        <v>142.9626234354567</v>
       </c>
       <c r="H268" t="n">
-        <v>160.8725373614707</v>
+        <v>160.8601717076303</v>
       </c>
       <c r="I268" t="n">
-        <v>153.9593263425682</v>
+        <v>154.1076159075951</v>
       </c>
       <c r="J268" t="n">
-        <v>194.3988353947196</v>
+        <v>194.443926079235</v>
       </c>
       <c r="K268" t="n">
-        <v>209.2972056417622</v>
+        <v>209.2732331242449</v>
       </c>
       <c r="L268" t="n">
-        <v>159.0295700404332</v>
+        <v>159.0157075529965</v>
       </c>
       <c r="M268" t="n">
         <v>159.2247848326065</v>
       </c>
       <c r="N268" t="n">
-        <v>172.4112048207235</v>
+        <v>172.3756794656005</v>
       </c>
       <c r="O268" t="n">
-        <v>191.5843627097533</v>
+        <v>191.5030779193627</v>
       </c>
       <c r="P268" t="n">
-        <v>139.6724386361362</v>
+        <v>139.6423599785755</v>
       </c>
       <c r="Q268" t="n">
-        <v>182.4768806795517</v>
+        <v>182.611501610083</v>
       </c>
     </row>
     <row r="269">
@@ -14680,52 +14680,52 @@
         <v>46113</v>
       </c>
       <c r="B269" t="n">
-        <v>238.3117597791225</v>
+        <v>238.8085528015461</v>
       </c>
       <c r="C269" t="n">
-        <v>121.9524723828205</v>
+        <v>121.9538935003732</v>
       </c>
       <c r="D269" t="n">
-        <v>135.9937046444603</v>
+        <v>135.9948802643655</v>
       </c>
       <c r="E269" t="n">
-        <v>115.7820705778394</v>
+        <v>115.8165663918324</v>
       </c>
       <c r="F269" t="n">
-        <v>138.8348830255531</v>
+        <v>138.7750543192678</v>
       </c>
       <c r="G269" t="n">
-        <v>130.3995906523599</v>
+        <v>130.2618065079076</v>
       </c>
       <c r="H269" t="n">
-        <v>157.6773478577342</v>
+        <v>157.6959028480466</v>
       </c>
       <c r="I269" t="n">
-        <v>127.711458644035</v>
+        <v>127.1268890717533</v>
       </c>
       <c r="J269" t="n">
-        <v>193.7167400801393</v>
+        <v>193.7877457901013</v>
       </c>
       <c r="K269" t="n">
-        <v>205.5856435056562</v>
+        <v>205.5714896549666</v>
       </c>
       <c r="L269" t="n">
-        <v>160.869437333392</v>
+        <v>160.8865384846897</v>
       </c>
       <c r="M269" t="n">
         <v>158.5272174316402</v>
       </c>
       <c r="N269" t="n">
-        <v>171.5477024593491</v>
+        <v>171.5928990747445</v>
       </c>
       <c r="O269" t="n">
-        <v>195.2933044170662</v>
+        <v>195.3286454353799</v>
       </c>
       <c r="P269" t="n">
-        <v>120.1173453775999</v>
+        <v>120.7272310933029</v>
       </c>
       <c r="Q269" t="n">
-        <v>186.7644361333424</v>
+        <v>186.7936899038833</v>
       </c>
     </row>
     <row r="270">
@@ -14733,52 +14733,52 @@
         <v>46143</v>
       </c>
       <c r="B270" t="n">
-        <v>298.181262789865</v>
+        <v>298.12615142023</v>
       </c>
       <c r="C270" t="n">
-        <v>116.157611344041</v>
+        <v>116.1579302319678</v>
       </c>
       <c r="D270" t="n">
-        <v>145.2730164413763</v>
+        <v>145.2725446635645</v>
       </c>
       <c r="E270" t="n">
-        <v>114.3661288204209</v>
+        <v>114.3921880135532</v>
       </c>
       <c r="F270" t="n">
-        <v>160.251102118232</v>
+        <v>160.2413068719029</v>
       </c>
       <c r="G270" t="n">
-        <v>124.0813831350022</v>
+        <v>124.1019547684525</v>
       </c>
       <c r="H270" t="n">
-        <v>157.6861642049587</v>
+        <v>157.7047139728698</v>
       </c>
       <c r="I270" t="n">
-        <v>163.463320716245</v>
+        <v>163.4587248122122</v>
       </c>
       <c r="J270" t="n">
-        <v>197.9439402580707</v>
+        <v>197.9065066227763</v>
       </c>
       <c r="K270" t="n">
-        <v>181.3161713282833</v>
+        <v>181.3355244629356</v>
       </c>
       <c r="L270" t="n">
-        <v>159.9041675519236</v>
+        <v>159.8839485183227</v>
       </c>
       <c r="M270" t="n">
         <v>158.527794469303</v>
       </c>
       <c r="N270" t="n">
-        <v>172.1575981486472</v>
+        <v>172.1696236256405</v>
       </c>
       <c r="O270" t="n">
-        <v>197.6246633593085</v>
+        <v>197.6998254133207</v>
       </c>
       <c r="P270" t="n">
-        <v>116.6721644492145</v>
+        <v>116.5094856865123</v>
       </c>
       <c r="Q270" t="n">
-        <v>179.4382752881308</v>
+        <v>179.3382764769599</v>
       </c>
     </row>
     <row r="271">
@@ -14786,52 +14786,52 @@
         <v>46174</v>
       </c>
       <c r="B271" t="n">
-        <v>208.3457968374464</v>
+        <v>207.9041151846568</v>
       </c>
       <c r="C271" t="n">
-        <v>327.5662163539745</v>
+        <v>327.5644763484944</v>
       </c>
       <c r="D271" t="n">
-        <v>140.8236785836511</v>
+        <v>140.8229747415578</v>
       </c>
       <c r="E271" t="n">
-        <v>118.6957896556949</v>
+        <v>118.6352346485697</v>
       </c>
       <c r="F271" t="n">
-        <v>161.3423016812092</v>
+        <v>161.4119256338224</v>
       </c>
       <c r="G271" t="n">
-        <v>127.9095155098097</v>
+        <v>128.0267280208125</v>
       </c>
       <c r="H271" t="n">
-        <v>160.513754239753</v>
+        <v>160.4766494815295</v>
       </c>
       <c r="I271" t="n">
-        <v>191.6760873347553</v>
+        <v>192.2652528110698</v>
       </c>
       <c r="J271" t="n">
-        <v>192.4240827146598</v>
+        <v>192.390510639992</v>
       </c>
       <c r="K271" t="n">
-        <v>195.6046134629763</v>
+        <v>195.5994141790137</v>
       </c>
       <c r="L271" t="n">
-        <v>163.0771483658405</v>
+        <v>163.0802662481435</v>
       </c>
       <c r="M271" t="n">
         <v>159.3951829641555</v>
       </c>
       <c r="N271" t="n">
-        <v>173.2653335647168</v>
+        <v>173.2081114723275</v>
       </c>
       <c r="O271" t="n">
-        <v>204.7794406070384</v>
+        <v>204.6689375347117</v>
       </c>
       <c r="P271" t="n">
-        <v>118.7250861855202</v>
+        <v>118.2778792325186</v>
       </c>
       <c r="Q271" t="n">
-        <v>178.1791322365433</v>
+        <v>178.2498772771747</v>
       </c>
     </row>
     <row r="272">
@@ -14839,52 +14839,105 @@
         <v>46204</v>
       </c>
       <c r="B272" t="n">
-        <v>119.6509197595139</v>
+        <v>120.0849467064038</v>
       </c>
       <c r="C272" t="n">
-        <v>407.2544500057287</v>
+        <v>407.2483259672136</v>
       </c>
       <c r="D272" t="n">
-        <v>139.3873976660967</v>
+        <v>139.9838720660817</v>
       </c>
       <c r="E272" t="n">
-        <v>119.1344115501932</v>
+        <v>119.0934603710032</v>
       </c>
       <c r="F272" t="n">
-        <v>164.8051246482998</v>
+        <v>165.6961918179227</v>
       </c>
       <c r="G272" t="n">
-        <v>127.4686113828202</v>
+        <v>128.2002132338324</v>
       </c>
       <c r="H272" t="n">
-        <v>146.5752782170304</v>
+        <v>146.5989097826353</v>
       </c>
       <c r="I272" t="n">
-        <v>170.2078485278293</v>
+        <v>171.8312938061768</v>
       </c>
       <c r="J272" t="n">
-        <v>185.6441492143441</v>
+        <v>184.1076147832328</v>
       </c>
       <c r="K272" t="n">
-        <v>189.8666349122454</v>
+        <v>189.8329854505796</v>
       </c>
       <c r="L272" t="n">
-        <v>158.5618049348616</v>
+        <v>158.4082476438141</v>
       </c>
       <c r="M272" t="n">
-        <v>159.0009296047849</v>
+        <v>158.726811443252</v>
       </c>
       <c r="N272" t="n">
-        <v>173.4134488729909</v>
+        <v>173.2965006998585</v>
       </c>
       <c r="O272" t="n">
-        <v>187.6185397240285</v>
+        <v>186.1257252362401</v>
       </c>
       <c r="P272" t="n">
-        <v>131.4148293697087</v>
+        <v>131.5378447133807</v>
       </c>
       <c r="Q272" t="n">
-        <v>177.9742728494024</v>
+        <v>177.9895031702264</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="2" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B273" t="n">
+        <v>77.52854618557996</v>
+      </c>
+      <c r="C273" t="n">
+        <v>247.1364200988062</v>
+      </c>
+      <c r="D273" t="n">
+        <v>141.441739933932</v>
+      </c>
+      <c r="E273" t="n">
+        <v>118.7477989312276</v>
+      </c>
+      <c r="F273" t="n">
+        <v>159.082051493254</v>
+      </c>
+      <c r="G273" t="n">
+        <v>133.3939896401508</v>
+      </c>
+      <c r="H273" t="n">
+        <v>146.8120057253329</v>
+      </c>
+      <c r="I273" t="n">
+        <v>187.5173817839257</v>
+      </c>
+      <c r="J273" t="n">
+        <v>179.4232188876325</v>
+      </c>
+      <c r="K273" t="n">
+        <v>195.4323247708166</v>
+      </c>
+      <c r="L273" t="n">
+        <v>159.7341413537492</v>
+      </c>
+      <c r="M273" t="n">
+        <v>158.046441144988</v>
+      </c>
+      <c r="N273" t="n">
+        <v>172.8928910951253</v>
+      </c>
+      <c r="O273" t="n">
+        <v>186.2780399165583</v>
+      </c>
+      <c r="P273" t="n">
+        <v>125.289847740708</v>
+      </c>
+      <c r="Q273" t="n">
+        <v>177.9551565692367</v>
       </c>
     </row>
   </sheetData>
@@ -14957,7 +15010,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-16T20:25:54Z</t>
+          <t>2026-10-21T19:38:26Z</t>
         </is>
       </c>
     </row>
@@ -14969,7 +15022,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
     </row>
